--- a/CVA Template.xlsx
+++ b/CVA Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Apps\ToolboxV.2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\matn0002\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2634739-89C6-47CC-A951-0EC3A0F35942}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFC440AA-E942-4347-8311-3EFF5D2435FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{B18F3221-7485-4E63-9676-B9068FAE1CCA}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B18F3221-7485-4E63-9676-B9068FAE1CCA}"/>
   </bookViews>
   <sheets>
     <sheet name="CondA_Baseline" sheetId="1" r:id="rId1"/>
@@ -38,9 +38,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="7">
   <si>
-    <t>reBAP</t>
-  </si>
-  <si>
     <t>PETCO2</t>
   </si>
   <si>
@@ -53,10 +50,13 @@
     <t>ECG</t>
   </si>
   <si>
-    <t>MCAv</t>
+    <t xml:space="preserve">ECG </t>
   </si>
   <si>
-    <t xml:space="preserve">ECG </t>
+    <t>MAP</t>
+  </si>
+  <si>
+    <t>CBFv</t>
   </si>
 </sst>
 </file>
@@ -923,22 +923,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>2</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -953,22 +953,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>2</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -983,22 +983,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>2</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -1013,22 +1013,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>2</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -1037,21 +1037,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100962EBB8201E715409E7E20DDF7FC46C3" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="f69b8aa37e68222bf0f2b68d7bee7b9d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="bd6218f0-02fb-4d57-9a72-659cc88aa709" xmlns:ns3="62e718d4-da4d-418e-bf30-5b87cbee8c16" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4e5f3794bb7ab5661d367a8067c94395" ns2:_="" ns3:_="">
     <xsd:import namespace="bd6218f0-02fb-4d57-9a72-659cc88aa709"/>
@@ -1286,24 +1271,22 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ADFEE463-46E2-4E57-BD8A-AB68CBAEC662}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{290BCE54-5EFB-4489-886C-83C78AABFFD1}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DCE852E5-C35E-4BB6-BD71-14DB1E3135F8}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1320,4 +1303,21 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{290BCE54-5EFB-4489-886C-83C78AABFFD1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ADFEE463-46E2-4E57-BD8A-AB68CBAEC662}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>